--- a/scratch/api_test_inv.xlsx
+++ b/scratch/api_test_inv.xlsx
@@ -370,7 +370,7 @@
     <row r="3">
       <c r="A3" t="inlineStr" s="0">
         <is>
-          <t>Generated: 01 Oct 2026 at 01:19 AM</t>
+          <t>Generated: 01 Oct 2026 at 01:32 AM</t>
         </is>
       </c>
     </row>
